--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588020</v>
+        <v>113588005</v>
       </c>
       <c r="B2" t="n">
-        <v>95994</v>
+        <v>80095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R2" t="n">
-        <v>6561395</v>
+        <v>6561348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +768,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587990</v>
+        <v>113588043</v>
       </c>
       <c r="B3" t="n">
-        <v>90053</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,26 +802,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346224</v>
+        <v>346256</v>
       </c>
       <c r="R3" t="n">
-        <v>6561347</v>
+        <v>6561406</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588005</v>
+        <v>113588040</v>
       </c>
       <c r="B5" t="n">
-        <v>80095</v>
+        <v>93892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,30 +1031,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346236</v>
+        <v>346270</v>
       </c>
       <c r="R5" t="n">
-        <v>6561348</v>
+        <v>6561401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1113,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1125,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113587931</v>
+        <v>113588020</v>
       </c>
       <c r="B6" t="n">
-        <v>104426</v>
+        <v>95994</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,28 +1147,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1173,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346184</v>
+        <v>346270</v>
       </c>
       <c r="R6" t="n">
-        <v>6561289</v>
+        <v>6561395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,6 +1222,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1236,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588040</v>
+        <v>113588055</v>
       </c>
       <c r="B7" t="n">
-        <v>93892</v>
+        <v>90053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,27 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346270</v>
+        <v>346232</v>
       </c>
       <c r="R7" t="n">
-        <v>6561401</v>
+        <v>6561393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,11 +1333,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588043</v>
+        <v>113587990</v>
       </c>
       <c r="B8" t="n">
-        <v>5164</v>
+        <v>90053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,32 +1365,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346256</v>
+        <v>346224</v>
       </c>
       <c r="R8" t="n">
-        <v>6561406</v>
+        <v>6561347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113588055</v>
+        <v>113587931</v>
       </c>
       <c r="B9" t="n">
-        <v>90053</v>
+        <v>104426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,26 +1486,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346232</v>
+        <v>346184</v>
       </c>
       <c r="R9" t="n">
-        <v>6561393</v>
+        <v>6561289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588005</v>
+        <v>113588040</v>
       </c>
       <c r="B2" t="n">
-        <v>80095</v>
+        <v>93900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346236</v>
+        <v>346270</v>
       </c>
       <c r="R2" t="n">
-        <v>6561348</v>
+        <v>6561401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113588043</v>
+        <v>113587967</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>90080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,32 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346256</v>
+        <v>346210</v>
       </c>
       <c r="R3" t="n">
-        <v>6561406</v>
+        <v>6561322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,21 +877,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -913,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587967</v>
+        <v>113588020</v>
       </c>
       <c r="B4" t="n">
-        <v>90073</v>
+        <v>96001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +909,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346210</v>
+        <v>346270</v>
       </c>
       <c r="R4" t="n">
-        <v>6561322</v>
+        <v>6561395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,6 +984,11 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588040</v>
+        <v>113588005</v>
       </c>
       <c r="B5" t="n">
-        <v>93892</v>
+        <v>80102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,31 +1017,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R5" t="n">
-        <v>6561401</v>
+        <v>6561348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1098,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1131,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588020</v>
+        <v>113587931</v>
       </c>
       <c r="B6" t="n">
-        <v>95994</v>
+        <v>104433</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,24 +1132,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1175,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346270</v>
+        <v>346184</v>
       </c>
       <c r="R6" t="n">
-        <v>6561395</v>
+        <v>6561289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,11 +1211,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1246,7 +1230,7 @@
         <v>113588055</v>
       </c>
       <c r="B7" t="n">
-        <v>90053</v>
+        <v>90060</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,7 +1336,7 @@
         <v>113587990</v>
       </c>
       <c r="B8" t="n">
-        <v>90053</v>
+        <v>90060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113587931</v>
+        <v>113588043</v>
       </c>
       <c r="B9" t="n">
-        <v>104426</v>
+        <v>5164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,31 +1470,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1518,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346184</v>
+        <v>346256</v>
       </c>
       <c r="R9" t="n">
-        <v>6561289</v>
+        <v>6561406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,6 +1550,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -1227,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588055</v>
+        <v>113587990</v>
       </c>
       <c r="B7" t="n">
         <v>90060</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346232</v>
+        <v>346224</v>
       </c>
       <c r="R7" t="n">
-        <v>6561393</v>
+        <v>6561347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,6 +1317,21 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1333,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113587990</v>
+        <v>113588055</v>
       </c>
       <c r="B8" t="n">
         <v>90060</v>
@@ -1376,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346224</v>
+        <v>346232</v>
       </c>
       <c r="R8" t="n">
-        <v>6561347</v>
+        <v>6561393</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,21 +1438,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588040</v>
+        <v>113587967</v>
       </c>
       <c r="B2" t="n">
-        <v>93900</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346270</v>
+        <v>346210</v>
       </c>
       <c r="R2" t="n">
-        <v>6561401</v>
+        <v>6561322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,11 +765,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587967</v>
+        <v>113587990</v>
       </c>
       <c r="B3" t="n">
-        <v>90080</v>
+        <v>90063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346210</v>
+        <v>346224</v>
       </c>
       <c r="R3" t="n">
-        <v>6561322</v>
+        <v>6561347</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +871,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -896,7 +905,7 @@
         <v>113588020</v>
       </c>
       <c r="B4" t="n">
-        <v>96001</v>
+        <v>96006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1005,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588005</v>
+        <v>113587931</v>
       </c>
       <c r="B5" t="n">
-        <v>80102</v>
+        <v>104438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,30 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346236</v>
+        <v>346184</v>
       </c>
       <c r="R5" t="n">
-        <v>6561348</v>
+        <v>6561289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1109,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Gammal tallstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1116,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113587931</v>
+        <v>113588005</v>
       </c>
       <c r="B6" t="n">
-        <v>104433</v>
+        <v>80104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,35 +1137,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346184</v>
+        <v>346236</v>
       </c>
       <c r="R6" t="n">
-        <v>6561289</v>
+        <v>6561348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,6 +1215,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1227,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113587990</v>
+        <v>113588055</v>
       </c>
       <c r="B7" t="n">
-        <v>90060</v>
+        <v>90063</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346224</v>
+        <v>346232</v>
       </c>
       <c r="R7" t="n">
-        <v>6561347</v>
+        <v>6561393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,21 +1326,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588055</v>
+        <v>113588040</v>
       </c>
       <c r="B8" t="n">
-        <v>90060</v>
+        <v>93905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,26 +1358,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346232</v>
+        <v>346270</v>
       </c>
       <c r="R8" t="n">
-        <v>6561393</v>
+        <v>6561401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,6 +1433,11 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113587967</v>
+        <v>113588020</v>
       </c>
       <c r="B2" t="n">
-        <v>90083</v>
+        <v>96034</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346210</v>
+        <v>346270</v>
       </c>
       <c r="R2" t="n">
-        <v>6561322</v>
+        <v>6561395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +766,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -784,7 +790,7 @@
         <v>113587990</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
+        <v>90094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113588020</v>
+        <v>113587967</v>
       </c>
       <c r="B4" t="n">
-        <v>96006</v>
+        <v>90114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,27 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346270</v>
+        <v>346210</v>
       </c>
       <c r="R4" t="n">
-        <v>6561395</v>
+        <v>6561322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,11 +998,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113587931</v>
+        <v>113588055</v>
       </c>
       <c r="B5" t="n">
-        <v>104438</v>
+        <v>90094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1030,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346184</v>
+        <v>346232</v>
       </c>
       <c r="R5" t="n">
-        <v>6561289</v>
+        <v>6561393</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588005</v>
+        <v>113587931</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>104468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,30 +1132,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346236</v>
+        <v>346184</v>
       </c>
       <c r="R6" t="n">
-        <v>6561348</v>
+        <v>6561289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1215,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Gammal tallstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1236,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588055</v>
+        <v>113588005</v>
       </c>
       <c r="B7" t="n">
-        <v>90063</v>
+        <v>80132</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346232</v>
+        <v>346236</v>
       </c>
       <c r="R7" t="n">
-        <v>6561393</v>
+        <v>6561348</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,6 +1321,11 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1345,7 +1345,7 @@
         <v>113588040</v>
       </c>
       <c r="B8" t="n">
-        <v>93905</v>
+        <v>93932</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588020</v>
+        <v>113587967</v>
       </c>
       <c r="B2" t="n">
-        <v>96034</v>
+        <v>90115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346270</v>
+        <v>346210</v>
       </c>
       <c r="R2" t="n">
-        <v>6561395</v>
+        <v>6561322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,11 +765,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,7 +784,7 @@
         <v>113587990</v>
       </c>
       <c r="B3" t="n">
-        <v>90094</v>
+        <v>90095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587967</v>
+        <v>113588055</v>
       </c>
       <c r="B4" t="n">
-        <v>90114</v>
+        <v>90095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346210</v>
+        <v>346232</v>
       </c>
       <c r="R4" t="n">
-        <v>6561322</v>
+        <v>6561393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588055</v>
+        <v>113588005</v>
       </c>
       <c r="B5" t="n">
-        <v>90094</v>
+        <v>80132</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346232</v>
+        <v>346236</v>
       </c>
       <c r="R5" t="n">
-        <v>6561393</v>
+        <v>6561348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1098,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1231,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588005</v>
+        <v>113588020</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>96034</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,30 +1242,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346236</v>
+        <v>346270</v>
       </c>
       <c r="R7" t="n">
-        <v>6561348</v>
+        <v>6561395</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113587967</v>
+        <v>113588020</v>
       </c>
       <c r="B2" t="n">
-        <v>90115</v>
+        <v>96038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346210</v>
+        <v>346270</v>
       </c>
       <c r="R2" t="n">
-        <v>6561322</v>
+        <v>6561395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +766,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587990</v>
+        <v>113587931</v>
       </c>
       <c r="B3" t="n">
-        <v>90095</v>
+        <v>104482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346224</v>
+        <v>346184</v>
       </c>
       <c r="R3" t="n">
-        <v>6561347</v>
+        <v>6561289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,21 +882,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113588055</v>
+        <v>113587990</v>
       </c>
       <c r="B4" t="n">
-        <v>90095</v>
+        <v>90099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346232</v>
+        <v>346224</v>
       </c>
       <c r="R4" t="n">
-        <v>6561393</v>
+        <v>6561347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +988,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588005</v>
+        <v>113588040</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>93936</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1031,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346236</v>
+        <v>346270</v>
       </c>
       <c r="R5" t="n">
-        <v>6561348</v>
+        <v>6561401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1113,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113587931</v>
+        <v>113587967</v>
       </c>
       <c r="B6" t="n">
-        <v>104468</v>
+        <v>90119</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1147,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346184</v>
+        <v>346210</v>
       </c>
       <c r="R6" t="n">
-        <v>6561289</v>
+        <v>6561322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588020</v>
+        <v>113588055</v>
       </c>
       <c r="B7" t="n">
-        <v>96034</v>
+        <v>90099</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,27 +1253,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346270</v>
+        <v>346232</v>
       </c>
       <c r="R7" t="n">
-        <v>6561395</v>
+        <v>6561393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,11 +1327,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1342,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588040</v>
+        <v>113588005</v>
       </c>
       <c r="B8" t="n">
-        <v>93932</v>
+        <v>80132</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,31 +1355,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R8" t="n">
-        <v>6561401</v>
+        <v>6561348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588020</v>
+        <v>113587990</v>
       </c>
       <c r="B2" t="n">
-        <v>96038</v>
+        <v>90099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346270</v>
+        <v>346224</v>
       </c>
       <c r="R2" t="n">
-        <v>6561395</v>
+        <v>6561347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,9 +766,19 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587931</v>
+        <v>113588040</v>
       </c>
       <c r="B3" t="n">
-        <v>104482</v>
+        <v>93936</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,28 +812,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -835,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346184</v>
+        <v>346270</v>
       </c>
       <c r="R3" t="n">
-        <v>6561289</v>
+        <v>6561401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +887,11 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -898,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587990</v>
+        <v>113587967</v>
       </c>
       <c r="B4" t="n">
-        <v>90099</v>
+        <v>90119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346224</v>
+        <v>346210</v>
       </c>
       <c r="R4" t="n">
-        <v>6561347</v>
+        <v>6561322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,21 +998,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588040</v>
+        <v>113587931</v>
       </c>
       <c r="B5" t="n">
-        <v>93936</v>
+        <v>104482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,24 +1030,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346270</v>
+        <v>346184</v>
       </c>
       <c r="R5" t="n">
-        <v>6561401</v>
+        <v>6561289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,11 +1109,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1131,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113587967</v>
+        <v>113588005</v>
       </c>
       <c r="B6" t="n">
-        <v>90119</v>
+        <v>80132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346210</v>
+        <v>346236</v>
       </c>
       <c r="R6" t="n">
-        <v>6561322</v>
+        <v>6561348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,6 +1215,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1237,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588055</v>
+        <v>113588020</v>
       </c>
       <c r="B7" t="n">
-        <v>90099</v>
+        <v>96038</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,26 +1252,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346232</v>
+        <v>346270</v>
       </c>
       <c r="R7" t="n">
-        <v>6561393</v>
+        <v>6561395</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,6 +1327,11 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1343,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588005</v>
+        <v>113588043</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>5164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,30 +1360,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1386,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346236</v>
+        <v>346256</v>
       </c>
       <c r="R8" t="n">
-        <v>6561348</v>
+        <v>6561406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,9 +1445,19 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1454,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113588043</v>
+        <v>113588055</v>
       </c>
       <c r="B9" t="n">
-        <v>5164</v>
+        <v>90099</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,32 +1491,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346256</v>
+        <v>346232</v>
       </c>
       <c r="R9" t="n">
-        <v>6561406</v>
+        <v>6561393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,21 +1565,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113587990</v>
+        <v>113588043</v>
       </c>
       <c r="B2" t="n">
-        <v>90099</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346224</v>
+        <v>346256</v>
       </c>
       <c r="R2" t="n">
-        <v>6561347</v>
+        <v>6561406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113588040</v>
+        <v>113588005</v>
       </c>
       <c r="B3" t="n">
-        <v>93936</v>
+        <v>80132</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +814,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R3" t="n">
-        <v>6561401</v>
+        <v>6561348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +895,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113587931</v>
+        <v>113588040</v>
       </c>
       <c r="B5" t="n">
-        <v>104482</v>
+        <v>93936</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,28 +1035,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1062,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346184</v>
+        <v>346270</v>
       </c>
       <c r="R5" t="n">
-        <v>6561289</v>
+        <v>6561401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,6 +1110,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1125,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588005</v>
+        <v>113588055</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>90099</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346236</v>
+        <v>346232</v>
       </c>
       <c r="R6" t="n">
-        <v>6561348</v>
+        <v>6561393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,11 +1221,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Gammal tallstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1236,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588020</v>
+        <v>113587931</v>
       </c>
       <c r="B7" t="n">
-        <v>96038</v>
+        <v>104482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,24 +1253,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346270</v>
+        <v>346184</v>
       </c>
       <c r="R7" t="n">
-        <v>6561395</v>
+        <v>6561289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,11 +1332,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588043</v>
+        <v>113588020</v>
       </c>
       <c r="B8" t="n">
-        <v>5164</v>
+        <v>96038</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,32 +1364,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346256</v>
+        <v>346270</v>
       </c>
       <c r="R8" t="n">
-        <v>6561406</v>
+        <v>6561395</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,19 +1440,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1475,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113588055</v>
+        <v>113587990</v>
       </c>
       <c r="B9" t="n">
         <v>90099</v>
@@ -1518,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346232</v>
+        <v>346224</v>
       </c>
       <c r="R9" t="n">
-        <v>6561393</v>
+        <v>6561347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,6 +1550,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588043</v>
+        <v>113587931</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>104482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346256</v>
+        <v>346184</v>
       </c>
       <c r="R2" t="n">
-        <v>6561406</v>
+        <v>6561289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,21 +770,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113588005</v>
+        <v>113587990</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>90099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346236</v>
+        <v>346224</v>
       </c>
       <c r="R3" t="n">
-        <v>6561348</v>
+        <v>6561347</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,9 +877,19 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1019,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588040</v>
+        <v>113588005</v>
       </c>
       <c r="B5" t="n">
-        <v>93936</v>
+        <v>80132</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,31 +1025,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R5" t="n">
-        <v>6561401</v>
+        <v>6561348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1106,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1131,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588055</v>
+        <v>113588020</v>
       </c>
       <c r="B6" t="n">
-        <v>90099</v>
+        <v>96038</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,26 +1140,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346232</v>
+        <v>346270</v>
       </c>
       <c r="R6" t="n">
-        <v>6561393</v>
+        <v>6561395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,6 +1215,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1237,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113587931</v>
+        <v>113588043</v>
       </c>
       <c r="B7" t="n">
-        <v>104482</v>
+        <v>5164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1252,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346184</v>
+        <v>346256</v>
       </c>
       <c r="R7" t="n">
-        <v>6561289</v>
+        <v>6561406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,6 +1332,21 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588020</v>
+        <v>113588040</v>
       </c>
       <c r="B8" t="n">
-        <v>96038</v>
+        <v>93936</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1379,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,7 +1410,7 @@
         <v>346270</v>
       </c>
       <c r="R8" t="n">
-        <v>6561395</v>
+        <v>6561401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113587990</v>
+        <v>113588055</v>
       </c>
       <c r="B9" t="n">
         <v>90099</v>
@@ -1503,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346224</v>
+        <v>346232</v>
       </c>
       <c r="R9" t="n">
-        <v>6561347</v>
+        <v>6561393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,21 +1565,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113587967</v>
+        <v>113588005</v>
       </c>
       <c r="B4" t="n">
-        <v>90119</v>
+        <v>80132</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346210</v>
+        <v>346236</v>
       </c>
       <c r="R4" t="n">
-        <v>6561322</v>
+        <v>6561348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,6 +997,11 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588005</v>
+        <v>113587967</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>90119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346236</v>
+        <v>346210</v>
       </c>
       <c r="R5" t="n">
-        <v>6561348</v>
+        <v>6561322</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,11 +1108,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Gammal tallstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113587931</v>
+        <v>113588005</v>
       </c>
       <c r="B2" t="n">
-        <v>104482</v>
+        <v>80132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346184</v>
+        <v>346236</v>
       </c>
       <c r="R2" t="n">
-        <v>6561289</v>
+        <v>6561348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,6 +765,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal tallstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113587990</v>
+        <v>113588040</v>
       </c>
       <c r="B3" t="n">
-        <v>90099</v>
+        <v>93936</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346224</v>
+        <v>346270</v>
       </c>
       <c r="R3" t="n">
-        <v>6561347</v>
+        <v>6561401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +878,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113588005</v>
+        <v>113587967</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>90119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346236</v>
+        <v>346210</v>
       </c>
       <c r="R4" t="n">
-        <v>6561348</v>
+        <v>6561322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +988,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Gammal tallstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1018,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113587967</v>
+        <v>113588020</v>
       </c>
       <c r="B5" t="n">
-        <v>90119</v>
+        <v>96038</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1020,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346210</v>
+        <v>346270</v>
       </c>
       <c r="R5" t="n">
-        <v>6561322</v>
+        <v>6561395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,6 +1095,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>berg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1124,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588020</v>
+        <v>113588043</v>
       </c>
       <c r="B6" t="n">
-        <v>96038</v>
+        <v>5164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,27 +1132,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346270</v>
+        <v>346256</v>
       </c>
       <c r="R6" t="n">
-        <v>6561395</v>
+        <v>6561406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,9 +1213,19 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1236,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113588043</v>
+        <v>113587931</v>
       </c>
       <c r="B7" t="n">
-        <v>5164</v>
+        <v>104482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,32 +1259,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346256</v>
+        <v>346184</v>
       </c>
       <c r="R7" t="n">
-        <v>6561406</v>
+        <v>6561289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,21 +1338,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113588040</v>
+        <v>113587990</v>
       </c>
       <c r="B8" t="n">
-        <v>93936</v>
+        <v>90099</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,27 +1370,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346270</v>
+        <v>346224</v>
       </c>
       <c r="R8" t="n">
-        <v>6561401</v>
+        <v>6561347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,9 +1445,19 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113588040</v>
+        <v>113588005</v>
       </c>
       <c r="B2" t="n">
-        <v>94158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346270</v>
+        <v>346236</v>
       </c>
       <c r="R2" t="n">
-        <v>6561400</v>
+        <v>6561348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +763,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>berg</t>
+          <t>Gammal tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113588043</v>
+        <v>113588020</v>
       </c>
       <c r="B3" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,32 +792,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346256</v>
+        <v>346271</v>
       </c>
       <c r="R3" t="n">
-        <v>6561406</v>
+        <v>6561394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +868,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,42 +888,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113588005</v>
+        <v>113588040</v>
       </c>
       <c r="B4" t="n">
-        <v>80429</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346236</v>
+        <v>346270</v>
       </c>
       <c r="R4" t="n">
-        <v>6561348</v>
+        <v>6561400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +977,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gammal tallstubbe</t>
+          <t>berg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,15 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113588020</v>
+        <v>113587967</v>
       </c>
       <c r="B5" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,27 +1006,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346271</v>
+        <v>346210</v>
       </c>
       <c r="R5" t="n">
-        <v>6561394</v>
+        <v>6561322</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,11 +1080,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>berg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113588055</v>
+        <v>113587990</v>
       </c>
       <c r="B6" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346233</v>
+        <v>346224</v>
       </c>
       <c r="R6" t="n">
-        <v>6561393</v>
+        <v>6561347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,6 +1181,21 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1243,15 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113587990</v>
+        <v>113588055</v>
       </c>
       <c r="B7" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346224</v>
+        <v>346233</v>
       </c>
       <c r="R7" t="n">
-        <v>6561347</v>
+        <v>6561393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,21 +1297,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1364,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113587967</v>
+        <v>113588043</v>
       </c>
       <c r="B8" t="n">
-        <v>90316</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,26 +1324,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346210</v>
+        <v>346256</v>
       </c>
       <c r="R8" t="n">
-        <v>6561322</v>
+        <v>6561406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,6 +1404,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,12 +1438,7 @@
         <v>113587931</v>
       </c>
       <c r="B9" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113588005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113588020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113588040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113587967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113587990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113588055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113588043</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,8 +1578,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113587931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>